--- a/data/TPS.MI.xlsx
+++ b/data/TPS.MI.xlsx
@@ -55572,6 +55572,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2401">
+      <c r="A2401" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B2401" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2401" t="n">
+        <v>8.05000019073486</v>
+      </c>
+      <c r="D2401" t="n">
+        <v>8.05000019073486</v>
+      </c>
+      <c r="E2401" t="n">
+        <v>8.05000019073486</v>
+      </c>
+      <c r="F2401" t="n">
+        <v>8.05000019073486</v>
+      </c>
+      <c r="G2401" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2402">
+      <c r="A2402" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2402" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C2402" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="D2402" t="n">
+        <v>8.14999961853027</v>
+      </c>
+      <c r="E2402" t="n">
+        <v>8.14999961853027</v>
+      </c>
+      <c r="F2402" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="G2402" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPS.MI.xlsx
+++ b/data/TPS.MI.xlsx
@@ -55618,6 +55618,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2403">
+      <c r="A2403" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2403" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2403" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="D2403" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="E2403" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="F2403" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="G2403" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2404">
+      <c r="A2404" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2404" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2404" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="D2404" t="n">
+        <v>8.14999961853027</v>
+      </c>
+      <c r="E2404" t="n">
+        <v>8.14999961853027</v>
+      </c>
+      <c r="F2404" t="n">
+        <v>7.94999980926514</v>
+      </c>
+      <c r="G2404" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPS.MI.xlsx
+++ b/data/TPS.MI.xlsx
@@ -55649,18 +55649,41 @@
         <v>500</v>
       </c>
       <c r="C2404" t="n">
-        <v>8.19999980926514</v>
+        <v>7.94999980926514</v>
       </c>
       <c r="D2404" t="n">
-        <v>8.14999961853027</v>
+        <v>7.94999980926514</v>
       </c>
       <c r="E2404" t="n">
-        <v>8.14999961853027</v>
+        <v>7.94999980926514</v>
       </c>
       <c r="F2404" t="n">
         <v>7.94999980926514</v>
       </c>
       <c r="G2404" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2405">
+      <c r="A2405" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2405" t="n">
+        <v>28500</v>
+      </c>
+      <c r="C2405" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="D2405" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2405" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2405" t="n">
+        <v>8.69999980926514</v>
+      </c>
+      <c r="G2405" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TPS.MI.xlsx
+++ b/data/TPS.MI.xlsx
@@ -55505,22 +55505,22 @@
     </row>
     <row r="2398">
       <c r="A2398" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2398" t="n">
         <v>500</v>
       </c>
       <c r="C2398" t="n">
-        <v>7.90000009536743</v>
+        <v>8</v>
       </c>
       <c r="D2398" t="n">
-        <v>7.90000009536743</v>
+        <v>8</v>
       </c>
       <c r="E2398" t="n">
-        <v>7.90000009536743</v>
+        <v>8</v>
       </c>
       <c r="F2398" t="n">
-        <v>7.90000009536743</v>
+        <v>8</v>
       </c>
       <c r="G2398" t="s">
         <v>7</v>
@@ -55528,13 +55528,13 @@
     </row>
     <row r="2399">
       <c r="A2399" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2399" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="C2399" t="n">
-        <v>8.14999961853027</v>
+        <v>7.90000009536743</v>
       </c>
       <c r="D2399" t="n">
         <v>7.90000009536743</v>
@@ -55543,7 +55543,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="F2399" t="n">
-        <v>8.14999961853027</v>
+        <v>7.90000009536743</v>
       </c>
       <c r="G2399" t="s">
         <v>7</v>
@@ -55551,22 +55551,22 @@
     </row>
     <row r="2400">
       <c r="A2400" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2400" t="n">
-        <v>4500</v>
+        <v>2000</v>
       </c>
       <c r="C2400" t="n">
-        <v>8.05000019073486</v>
+        <v>8.14999961853027</v>
       </c>
       <c r="D2400" t="n">
-        <v>7.84999990463257</v>
+        <v>7.90000009536743</v>
       </c>
       <c r="E2400" t="n">
-        <v>8</v>
+        <v>7.90000009536743</v>
       </c>
       <c r="F2400" t="n">
-        <v>8.05000019073486</v>
+        <v>8.14999961853027</v>
       </c>
       <c r="G2400" t="s">
         <v>7</v>
@@ -55574,19 +55574,19 @@
     </row>
     <row r="2401">
       <c r="A2401" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2401" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="C2401" t="n">
         <v>8.05000019073486</v>
       </c>
       <c r="D2401" t="n">
-        <v>8.05000019073486</v>
+        <v>7.84999990463257</v>
       </c>
       <c r="E2401" t="n">
-        <v>8.05000019073486</v>
+        <v>8</v>
       </c>
       <c r="F2401" t="n">
         <v>8.05000019073486</v>
@@ -55597,22 +55597,22 @@
     </row>
     <row r="2402">
       <c r="A2402" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2402" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="C2402" t="n">
-        <v>8.19999980926514</v>
+        <v>8.05000019073486</v>
       </c>
       <c r="D2402" t="n">
-        <v>8.14999961853027</v>
+        <v>8.05000019073486</v>
       </c>
       <c r="E2402" t="n">
-        <v>8.14999961853027</v>
+        <v>8.05000019073486</v>
       </c>
       <c r="F2402" t="n">
-        <v>8.19999980926514</v>
+        <v>8.05000019073486</v>
       </c>
       <c r="G2402" t="s">
         <v>7</v>
@@ -55620,19 +55620,19 @@
     </row>
     <row r="2403">
       <c r="A2403" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2403" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="C2403" t="n">
         <v>8.19999980926514</v>
       </c>
       <c r="D2403" t="n">
-        <v>8.19999980926514</v>
+        <v>8.14999961853027</v>
       </c>
       <c r="E2403" t="n">
-        <v>8.19999980926514</v>
+        <v>8.14999961853027</v>
       </c>
       <c r="F2403" t="n">
         <v>8.19999980926514</v>
@@ -55643,22 +55643,22 @@
     </row>
     <row r="2404">
       <c r="A2404" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2404" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="C2404" t="n">
-        <v>7.94999980926514</v>
+        <v>8.19999980926514</v>
       </c>
       <c r="D2404" t="n">
-        <v>7.94999980926514</v>
+        <v>8.19999980926514</v>
       </c>
       <c r="E2404" t="n">
-        <v>7.94999980926514</v>
+        <v>8.19999980926514</v>
       </c>
       <c r="F2404" t="n">
-        <v>7.94999980926514</v>
+        <v>8.19999980926514</v>
       </c>
       <c r="G2404" t="s">
         <v>7</v>
@@ -55666,24 +55666,47 @@
     </row>
     <row r="2405">
       <c r="A2405" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2405" t="n">
-        <v>28500</v>
+        <v>500</v>
       </c>
       <c r="C2405" t="n">
-        <v>8.75</v>
+        <v>7.94999980926514</v>
       </c>
       <c r="D2405" t="n">
-        <v>8</v>
+        <v>7.94999980926514</v>
       </c>
       <c r="E2405" t="n">
-        <v>8</v>
+        <v>7.94999980926514</v>
       </c>
       <c r="F2405" t="n">
-        <v>8.69999980926514</v>
+        <v>7.94999980926514</v>
       </c>
       <c r="G2405" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2406">
+      <c r="A2406" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2406" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2406" t="n">
+        <v>8.55000019073486</v>
+      </c>
+      <c r="D2406" t="n">
+        <v>8.55000019073486</v>
+      </c>
+      <c r="E2406" t="n">
+        <v>8.55000019073486</v>
+      </c>
+      <c r="F2406" t="n">
+        <v>8.55000019073486</v>
+      </c>
+      <c r="G2406" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TPS.MI.xlsx
+++ b/data/TPS.MI.xlsx
@@ -55894,6 +55894,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2415">
+      <c r="A2415" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2415" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2415" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="D2415" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="E2415" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="F2415" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="G2415" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2416">
+      <c r="A2416" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B2416" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C2416" t="n">
+        <v>8.14999961853027</v>
+      </c>
+      <c r="D2416" t="n">
+        <v>8.05000019073486</v>
+      </c>
+      <c r="E2416" t="n">
+        <v>8.05000019073486</v>
+      </c>
+      <c r="F2416"/>
+      <c r="G2416" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPS.MI.xlsx
+++ b/data/TPS.MI.xlsx
@@ -55963,6 +55963,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2418">
+      <c r="A2418" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B2418" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2418" t="n">
+        <v>8.05000019073486</v>
+      </c>
+      <c r="D2418" t="n">
+        <v>8.05000019073486</v>
+      </c>
+      <c r="E2418" t="n">
+        <v>8.05000019073486</v>
+      </c>
+      <c r="F2418" t="n">
+        <v>8.05000019073486</v>
+      </c>
+      <c r="G2418" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2419">
+      <c r="A2419" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2419" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C2419" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="D2419" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="E2419" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="F2419"/>
+      <c r="G2419" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPS.MI.xlsx
+++ b/data/TPS.MI.xlsx
@@ -56002,8 +56002,31 @@
       <c r="E2419" t="n">
         <v>8.10000038146973</v>
       </c>
-      <c r="F2419"/>
+      <c r="F2419" t="n">
+        <v>8.19999980926514</v>
+      </c>
       <c r="G2419" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2420">
+      <c r="A2420" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2420" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C2420" t="n">
+        <v>8.14999961853027</v>
+      </c>
+      <c r="D2420" t="n">
+        <v>8.05000019073486</v>
+      </c>
+      <c r="E2420" t="n">
+        <v>8.14999961853027</v>
+      </c>
+      <c r="F2420"/>
+      <c r="G2420" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TPS.MI.xlsx
+++ b/data/TPS.MI.xlsx
@@ -56025,7 +56025,9 @@
       <c r="E2420" t="n">
         <v>8.14999961853027</v>
       </c>
-      <c r="F2420"/>
+      <c r="F2420" t="n">
+        <v>8.14999961853027</v>
+      </c>
       <c r="G2420" t="s">
         <v>7</v>
       </c>

--- a/data/TPS.MI.xlsx
+++ b/data/TPS.MI.xlsx
@@ -56032,6 +56032,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2421">
+      <c r="A2421" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2421" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2421" t="n">
+        <v>8.14999961853027</v>
+      </c>
+      <c r="D2421" t="n">
+        <v>8.14999961853027</v>
+      </c>
+      <c r="E2421" t="n">
+        <v>8.14999961853027</v>
+      </c>
+      <c r="F2421" t="n">
+        <v>8.14999961853027</v>
+      </c>
+      <c r="G2421" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2422">
+      <c r="A2422" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2422" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2422" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2422" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2422" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2422"/>
+      <c r="G2422" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPS.MI.xlsx
+++ b/data/TPS.MI.xlsx
@@ -56078,6 +56078,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2423">
+      <c r="A2423" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2423" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2423" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2423" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2423" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2423" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2423" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPS.MI.xlsx
+++ b/data/TPS.MI.xlsx
@@ -56101,6 +56101,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2424">
+      <c r="A2424" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B2424" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2424" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2424" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2424" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2424" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2424" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPS.MI.xlsx
+++ b/data/TPS.MI.xlsx
@@ -56124,6 +56124,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2425">
+      <c r="A2425" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B2425" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2425" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2425" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2425" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2425" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2425" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPS.MI.xlsx
+++ b/data/TPS.MI.xlsx
@@ -56147,6 +56147,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2426">
+      <c r="A2426" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2426" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2426" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2426" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2426" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2426" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2426" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
